--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260707.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,154 +601,154 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>29,790,000</t>
+          <t>9,185,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>9,108,000</t>
+          <t>5,488,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>6,153,000</t>
+          <t>3,483,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>3,132,000</t>
+          <t>43,790,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2,863,000</t>
+          <t>10,293,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>39,956,000</t>
+          <t>32,516,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,868,000</t>
+          <t>19,101,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -770,799 +770,799 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>17,917,000</t>
+          <t>5,382,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>9,138,000</t>
+          <t>32,918,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>28,258,000</t>
+          <t>23,799,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>17,008,000</t>
+          <t>3,790,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3,371,000</t>
+          <t>2,609,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,368,000</t>
+          <t>28,640,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>27,323,000</t>
+          <t>19,313,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>20,671,000</t>
+          <t>17,008,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>27,418,000</t>
+          <t>1,946,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>32,659,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>5,190,000</t>
+          <t>8,532,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,731,000</t>
+          <t>8,456,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>633,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>16,434,000</t>
+          <t>13,608,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>28,364,000</t>
+          <t>3,670,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>7,617,000</t>
+          <t>19,261,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>5,983,000</t>
+          <t>12,938,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>4,986,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,724,000</t>
+          <t>16,240,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>17,149,000</t>
+          <t>13,206,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>7,344,000</t>
+          <t>12,723,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,187,000</t>
+          <t>36,477,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>11,547,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>11,511,000</t>
+          <t>5,983,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,856,000</t>
+          <t>21,675,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>8,716,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>11,991,000</t>
+          <t>3,334,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>31,628,000</t>
+          <t>8,771,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>19,449,000</t>
+          <t>8,699,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,150,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,861,000</t>
+          <t>8,065,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>19,641,000</t>
+          <t>475,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>405,000</t>
+          <t>17,290,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>7,440,000</t>
+          <t>44,393,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1579,716 +1579,210 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,032,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>16,692,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,385,637,177</t>
+          <t>6,553,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,798,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>37,237,000</t>
+          <t>1,314,897,177</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>45,888,000</t>
+          <t>15,796,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>14,406,000</t>
+          <t>16,216,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>長華電材</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>15,522,000</t>
+          <t>17,187,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>長華電材</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>15,755,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>572,000</t>
+          <t>-15,893,968,361</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>力成科技</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>2,092,000</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>文曄科技</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>1,234,000</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>台灣積體</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>76,000</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>0.13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>仁寶電腦</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>4,745,000</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>0.12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>宏碁股份</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>3,919,000</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>0.09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>和碩聯合</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>1,203,000</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>頎邦科技</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>246,000</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>群光電子</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>468,000</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>神基控股</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>400,000</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>家登精密</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>瑞儀光電</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>301,000</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>8454</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>富邦媒體</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>118,000</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>5388</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>中磊電子</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>95,000</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>8016</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>矽創電子</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>52,000</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>6561</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>是方電訊</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>31,000</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>2393</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>億光電子</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>166,000</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>美律實業</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>118,000</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>崑鼎綠能</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>6412</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>群光電能</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>67,000</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>6188</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>廣明光電</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>73,000</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>PB_NTD</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>-46,566,285</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>DA_NTD</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>-15,585,800,159</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>-10.96%</t>
+          <t>-11.55%</t>
         </is>
       </c>
     </row>
